--- a/data/analyse/eps_summary_stats.xlsx
+++ b/data/analyse/eps_summary_stats.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resume_General" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Statistiques_Descriptives" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Distribution_Anomalies" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Matrice_Correlation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="General_Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Descriptive_Statistics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Anomaly_Distribution" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Correlation_Matrix" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,24 +439,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Valeur</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Total Echantillons</t>
+          <t>Total Samples</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5963</v>
+        <v>5956</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Echantillons Normaux</t>
+          <t>Normal Samples</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -466,39 +466,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Echantillons Anormaux</t>
+          <t>Abnormal Samples</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>963</v>
+        <v>956</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Anomalies Critiques</t>
+          <t>Critical Anomalies</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Score Sante Batterie</t>
+          <t>Battery Health Score</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>80.2%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Score Stabilite Systeme</t>
+          <t>System Stability Score</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -510,19 +510,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Score Efficacite Solaire</t>
+          <t>Solar Efficiency Score</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.4%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Score Coherence Physique</t>
+          <t>Physical Consistency Score</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -599,31 +599,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5913</v>
+        <v>5906</v>
       </c>
       <c r="C2" t="n">
-        <v>5963</v>
+        <v>5956</v>
       </c>
       <c r="D2" t="n">
-        <v>5963</v>
+        <v>5956</v>
       </c>
       <c r="E2" t="n">
-        <v>5963</v>
+        <v>5956</v>
       </c>
       <c r="F2" t="n">
-        <v>5963</v>
+        <v>5956</v>
       </c>
       <c r="G2" t="n">
-        <v>5963</v>
+        <v>5956</v>
       </c>
       <c r="H2" t="n">
-        <v>5963</v>
+        <v>5956</v>
       </c>
       <c r="I2" t="n">
-        <v>5963</v>
+        <v>5956</v>
       </c>
       <c r="J2" t="n">
-        <v>5913</v>
+        <v>5906</v>
       </c>
     </row>
     <row r="3">
@@ -633,31 +633,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.805965837984104</v>
+        <v>7.810607856417202</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7495906422941471</v>
+        <v>0.7512033243787776</v>
       </c>
       <c r="D3" t="n">
-        <v>4.849404662082844</v>
+        <v>4.876645399597045</v>
       </c>
       <c r="E3" t="n">
-        <v>10.03720878752306</v>
+        <v>10.03848942243116</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7595061210799932</v>
+        <v>0.7500978844862325</v>
       </c>
       <c r="G3" t="n">
-        <v>7.694879590809996</v>
+        <v>7.696239758226997</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4891908435351333</v>
+        <v>0.4892718267293485</v>
       </c>
       <c r="I3" t="n">
-        <v>4.288680194532954</v>
+        <v>4.213045668233714</v>
       </c>
       <c r="J3" t="n">
-        <v>51.74747167258582</v>
+        <v>51.81581442600745</v>
       </c>
     </row>
     <row r="4">
@@ -667,31 +667,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4635022160822299</v>
+        <v>0.4600734557916171</v>
       </c>
       <c r="C4" t="n">
-        <v>1.33677760790214</v>
+        <v>1.324091076412594</v>
       </c>
       <c r="D4" t="n">
-        <v>17.94393625351294</v>
+        <v>17.90370755300675</v>
       </c>
       <c r="E4" t="n">
-        <v>7.669070126248571</v>
+        <v>7.687626311111925</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6730308804251111</v>
+        <v>0.6673065101542652</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5495306730977904</v>
+        <v>0.5470170865413039</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1518161830695516</v>
+        <v>0.1517835808015077</v>
       </c>
       <c r="I4" t="n">
-        <v>14.74424071752488</v>
+        <v>14.80167687615808</v>
       </c>
       <c r="J4" t="n">
-        <v>21.65807626202527</v>
+        <v>21.74818716274555</v>
       </c>
     </row>
     <row r="5">
@@ -704,25 +704,25 @@
         <v>5.995</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.994</v>
+        <v>-2.993</v>
       </c>
       <c r="D5" t="n">
         <v>-21.2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.609</v>
+        <v>0.599</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.027</v>
+        <v>-0.024</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>0.035</v>
+        <v>0.047</v>
       </c>
       <c r="I5" t="n">
-        <v>-16.9</v>
+        <v>-16.8</v>
       </c>
       <c r="J5" t="n">
         <v>10</v>
@@ -735,31 +735,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.475</v>
+        <v>7.47425</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.408</v>
+        <v>-0.4025</v>
       </c>
       <c r="D6" t="n">
         <v>-14.6</v>
       </c>
       <c r="E6" t="n">
-        <v>0.845</v>
+        <v>0.843</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>7.4295</v>
+        <v>7.419</v>
       </c>
       <c r="H6" t="n">
         <v>0.34</v>
       </c>
       <c r="I6" t="n">
-        <v>-12.15</v>
+        <v>-12.1</v>
       </c>
       <c r="J6" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="7">
@@ -769,31 +769,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.979</v>
+        <v>7.983</v>
       </c>
       <c r="C7" t="n">
-        <v>0.794</v>
+        <v>0.804</v>
       </c>
       <c r="D7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>15.359</v>
+        <v>15.409</v>
       </c>
       <c r="F7" t="n">
-        <v>0.722</v>
+        <v>0.7004999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>7.882</v>
+        <v>7.883</v>
       </c>
       <c r="H7" t="n">
-        <v>0.487</v>
+        <v>0.488</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>60.1</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="8">
@@ -803,31 +803,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.157999999999999</v>
+        <v>8.162000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>2.0915</v>
+        <v>2.06075</v>
       </c>
       <c r="D8" t="n">
         <v>18.7</v>
       </c>
       <c r="E8" t="n">
-        <v>16.677</v>
+        <v>16.716</v>
       </c>
       <c r="F8" t="n">
-        <v>1.387</v>
+        <v>1.351</v>
       </c>
       <c r="G8" t="n">
-        <v>8.066000000000001</v>
+        <v>8.06925</v>
       </c>
       <c r="H8" t="n">
-        <v>0.639</v>
+        <v>0.638</v>
       </c>
       <c r="I8" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="J8" t="n">
-        <v>70.09999999999999</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="9">
@@ -846,16 +846,16 @@
         <v>69.90000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>18.018</v>
+        <v>18.016</v>
       </c>
       <c r="F9" t="n">
-        <v>2.018</v>
+        <v>2.019</v>
       </c>
       <c r="G9" t="n">
-        <v>8.494999999999999</v>
+        <v>8.462999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.924</v>
+        <v>0.919</v>
       </c>
       <c r="I9" t="n">
         <v>75</v>
@@ -881,17 +881,17 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Type_Anomalie</t>
+          <t>Anomaly_Type</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Nombre</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Pourcentage</t>
+          <t>Percentage</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
         <v>5000</v>
       </c>
       <c r="C2" t="n">
-        <v>83.84999999999999</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="3">
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C3" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4">
@@ -996,33 +996,33 @@
         <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>battery_degradation</t>
+          <t>progressive_overheat</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>progressive_overheat</t>
+          <t>battery_degradation</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C11" t="n">
-        <v>1.01</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -1148,28 +1148,28 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6900981250460574</v>
+        <v>0.6858796281395833</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5383969009562891</v>
+        <v>0.5186106967313305</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7067282322229892</v>
+        <v>0.7000211175143853</v>
       </c>
       <c r="F2" t="n">
-        <v>0.622314553453327</v>
+        <v>0.616371667079728</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7676707755838077</v>
+        <v>0.7459522697541984</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1220520447155019</v>
+        <v>0.1046863953496362</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5785010865142657</v>
+        <v>0.5739203242928848</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8967445424005654</v>
+        <v>0.8865918285645423</v>
       </c>
     </row>
     <row r="3">
@@ -1179,31 +1179,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6900981250460574</v>
+        <v>0.6858796281395833</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4786015157841675</v>
+        <v>0.4743098055371085</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7555503247993209</v>
+        <v>0.7680545808445364</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8342889361948486</v>
+        <v>0.8496484763278092</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5020118898535681</v>
+        <v>0.4876934112187618</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04896764515140045</v>
+        <v>0.03325338630243316</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6325202356575762</v>
+        <v>0.6410088724962911</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7360203964009567</v>
+        <v>0.7391835812458021</v>
       </c>
     </row>
     <row r="4">
@@ -1213,31 +1213,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5383969009562891</v>
+        <v>0.5186106967313305</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4786015157841675</v>
+        <v>0.4743098055371085</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7722490331600464</v>
+        <v>0.7484259533570408</v>
       </c>
       <c r="F4" t="n">
-        <v>0.67106600330796</v>
+        <v>0.6500003123858238</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4362613622099943</v>
+        <v>0.4194090198464783</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0720035102581767</v>
+        <v>0.0665530969094663</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7560452868687131</v>
+        <v>0.7324375256509569</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6759175308212514</v>
+        <v>0.6616233758005921</v>
       </c>
     </row>
     <row r="5">
@@ -1247,31 +1247,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7067282322229892</v>
+        <v>0.7000211175143853</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7555503247993209</v>
+        <v>0.7680545808445364</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7722490331600464</v>
+        <v>0.7484259533570408</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8655029454868784</v>
+        <v>0.8612574800660191</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5411467121786588</v>
+        <v>0.526575818372179</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1665939552225607</v>
+        <v>0.1475806979866059</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7924448631940807</v>
+        <v>0.794452470124026</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8658188792488167</v>
+        <v>0.8687598137470603</v>
       </c>
     </row>
     <row r="6">
@@ -1281,31 +1281,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.622314553453327</v>
+        <v>0.616371667079728</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8342889361948486</v>
+        <v>0.8496484763278092</v>
       </c>
       <c r="D6" t="n">
-        <v>0.67106600330796</v>
+        <v>0.6500003123858238</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8655029454868784</v>
+        <v>0.8612574800660191</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4466373537495376</v>
+        <v>0.4365818868586805</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1434015788358073</v>
+        <v>0.13582979926144</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6991679567173109</v>
+        <v>0.6965553562317606</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7541679195533449</v>
+        <v>0.754743465452043</v>
       </c>
     </row>
     <row r="7">
@@ -1315,31 +1315,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7676707755838077</v>
+        <v>0.7459522697541984</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5020118898535681</v>
+        <v>0.4876934112187618</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4362613622099943</v>
+        <v>0.4194090198464783</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5411467121786588</v>
+        <v>0.526575818372179</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4466373537495376</v>
+        <v>0.4365818868586805</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05613144849470861</v>
+        <v>0.03582802666944979</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3107083608785655</v>
+        <v>0.3007311117462277</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7195266875215061</v>
+        <v>0.7045823276954724</v>
       </c>
     </row>
     <row r="8">
@@ -1349,31 +1349,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1220520447155019</v>
+        <v>0.1046863953496362</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04896764515140045</v>
+        <v>0.03325338630243316</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0720035102581767</v>
+        <v>0.0665530969094663</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1665939552225607</v>
+        <v>0.1475806979866059</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1434015788358073</v>
+        <v>0.13582979926144</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05613144849470861</v>
+        <v>0.03582802666944979</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06128305390436465</v>
+        <v>0.05191200039020753</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1515638063416569</v>
+        <v>0.1305157027577084</v>
       </c>
     </row>
     <row r="9">
@@ -1383,31 +1383,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5785010865142657</v>
+        <v>0.5739203242928848</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6325202356575762</v>
+        <v>0.6410088724962911</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7560452868687131</v>
+        <v>0.7324375256509569</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7924448631940807</v>
+        <v>0.794452470124026</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6991679567173109</v>
+        <v>0.6965553562317606</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3107083608785655</v>
+        <v>0.3007311117462277</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06128305390436465</v>
+        <v>0.05191200039020753</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7017015316487398</v>
+        <v>0.7061707926563985</v>
       </c>
     </row>
     <row r="10">
@@ -1417,28 +1417,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8967445424005654</v>
+        <v>0.8865918285645423</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7360203964009567</v>
+        <v>0.7391835812458021</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6759175308212514</v>
+        <v>0.6616233758005921</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8658188792488167</v>
+        <v>0.8687598137470603</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7541679195533449</v>
+        <v>0.754743465452043</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7195266875215061</v>
+        <v>0.7045823276954724</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1515638063416569</v>
+        <v>0.1305157027577084</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7017015316487398</v>
+        <v>0.7061707926563985</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
